--- a/privat24-skill/fixtures/sample_web.xlsx
+++ b/privat24-skill/fixtures/sample_web.xlsx
@@ -487,12 +487,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13.05.2026 11:08:00</t>
+          <t>13.05.2026 13:51:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Фонди та організації</t>
+          <t>Комуналка та Інтернет</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,11 +502,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Автоплатіж. Отримувач Тестовий фонд. Коментар: внесок</t>
+          <t>TEST UTILITY</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-1331.35</v>
+        <v>-1893.42</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1331.35</v>
+        <v>1893.42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-10427.73</v>
+        <v>-12085.42</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -533,12 +533,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13.05.2026 01:54:00</t>
+          <t>13.05.2026 08:13:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Комуналка та Інтернет</t>
+          <t>Зарахування переказу</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -548,11 +548,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TEST UTILITY</t>
+          <t>Test sender alpha</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-1893.42</v>
+        <v>-1140.21</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1893.42</v>
+        <v>1140.21</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-9096.379999999999</v>
+        <v>-10192</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -579,12 +579,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12.05.2026 20:16:00</t>
+          <t>12.05.2026 22:52:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Зарахування переказу</t>
+          <t>Кафе та ресторани</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -594,11 +594,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Test sender alpha</t>
+          <t>CAFE TEST, KYIV</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-1140.21</v>
+        <v>-1408.13</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1140.21</v>
+        <v>1408.13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-7202.96</v>
+        <v>-9051.790000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -625,12 +625,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12.05.2026 10:55:00</t>
+          <t>12.05.2026 22:14:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Кафе та ресторани</t>
+          <t>Фонди та організації</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,11 +640,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CAFE TEST, KYIV</t>
+          <t>Автоплатіж. Отримувач Тестовий фонд. Коментар: внесок</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-1408.13</v>
+        <v>-1450.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1408.13</v>
+        <v>1450.74</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-6062.75</v>
+        <v>-7643.66</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12.05.2026 10:17:00</t>
+          <t>12.05.2026 06:01:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Комуналка та Інтернет</t>
+          <t>Кафе та ресторани</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -686,11 +686,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TEST UTILITY</t>
+          <t>CAFE TEST, KYIV</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-1450.74</v>
+        <v>-1562.58</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1450.74</v>
+        <v>1562.58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-4654.62</v>
+        <v>-6192.92</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -717,12 +717,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11.05.2026 21:01:00</t>
+          <t>11.05.2026 15:22:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Перекази</t>
+          <t>Магазини</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -732,11 +732,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Test recipient beta</t>
+          <t>SHOP TEST 1, KYIV</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-1009.14</v>
+        <v>-1784.34</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1009.14</v>
+        <v>1784.34</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-3203.88</v>
+        <v>-4630.34</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -763,12 +763,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.05.2026 21:33:00</t>
+          <t>11.05.2026 11:23:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Кафе та ресторани</t>
+          <t>Комуналка та Інтернет</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -778,11 +778,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CAFE TEST, KYIV</t>
+          <t>TEST UTILITY</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-419.88</v>
+        <v>-124.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>419.88</v>
+        <v>124.01</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-2194.74</v>
+        <v>-2846</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.05.2026 19:42:00</t>
+          <t>10.05.2026 17:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Магазини</t>
+          <t>Перекази</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -824,11 +824,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SHOP TEST 1, KYIV</t>
+          <t>Test recipient beta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-238.81</v>
+        <v>-363.12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>238.81</v>
+        <v>363.12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-1774.86</v>
+        <v>-2721.99</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -855,12 +855,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.05.2026 11:58:00</t>
+          <t>10.05.2026 02:53:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Перекази</t>
+          <t>Сервіси</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -870,11 +870,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EUR transfer test</t>
+          <t>FREE FX TEST</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -882,15 +882,15 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>14.29</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-1536.05</v>
+        <v>-2358.87</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09.05.2026 23:22:00</t>
+          <t>09.05.2026 06:41:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Перекази</t>
+          <t>Фонди та організації</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Test recipient beta</t>
+          <t>Автоплатіж. Отримувач Тестовий фонд. Коментар: внесок</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1047.5</v>
+        <v>-1958.75</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1047.5</v>
+        <v>1958.75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-1336.05</v>
+        <v>-2358.87</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -947,12 +947,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09.05.2026 03:10:00</t>
+          <t>08.05.2026 22:01:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Фонди та організації</t>
+          <t>Комуналка та Інтернет</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -962,11 +962,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Автоплатіж. Отримувач Тестовий фонд. Коментар: внесок</t>
+          <t>TEST UTILITY</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-1958.75</v>
+        <v>-366.53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1958.75</v>
+        <v>366.53</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-2383.55</v>
+        <v>-400.12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -993,12 +993,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08.05.2026 18:30:00</t>
+          <t>07.05.2026 23:50:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Комуналка та Інтернет</t>
+          <t>Магазини</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1008,11 +1008,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEST UTILITY</t>
+          <t>SHOP TEST 2, KHARKIV</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-366.53</v>
+        <v>-1037.62</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>366.53</v>
+        <v>1037.62</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-424.8</v>
+        <v>-33.59</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1039,12 +1039,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07.05.2026 20:19:00</t>
+          <t>07.05.2026 12:51:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Магазини</t>
+          <t>Кафе та ресторани</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SHOP TEST 2, KHARKIV</t>
+          <t>CAFE TEST, KYIV</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-1037.62</v>
+        <v>-1487.32</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1037.62</v>
+        <v>1487.32</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-58.27</v>
+        <v>1004.03</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1085,12 +1085,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07.05.2026 09:20:00</t>
+          <t>07.05.2026 03:28:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Транспорт</t>
+          <t>Аптеки</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1100,11 +1100,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TRANSPORT TEST</t>
+          <t>APTEKA TEST, KYIV</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-1487.32</v>
+        <v>1052.12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1487.32</v>
+        <v>1052.12</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>979.35</v>
+        <v>2491.35</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Магазини</t>
+          <t>Перекази</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SHOP TEST 2, KHARKIV</t>
+          <t>EUR transfer test</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>827.4400000000001</v>
+        <v>-200</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1158,15 +1158,15 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>827.4400000000001</v>
+        <v>14.29</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2466.67</v>
+        <v>1439.23</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
